--- a/mapping.xlsx
+++ b/mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sh0tny1\рабочий стол\Yerlan\Автоматизация отчета в 1С\Код автоматизации\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF66101-3767-4226-95E4-87074E85CCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254793F7-DE59-4B8D-9A1B-761F24AB8EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -426,10 +426,10 @@
     <t>сумма × % из настроек (транспортировка)</t>
   </si>
   <si>
+    <t>новая статья, в старом отчёте не учтена</t>
+  </si>
+  <si>
     <t>Транспортно-экспедиционные расходы</t>
-  </si>
-  <si>
-    <t>новая статья, в старом отчёте не учтена</t>
   </si>
 </sst>
 </file>
@@ -2412,7 +2412,7 @@
         <v>7110</v>
       </c>
       <c r="B96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C96" t="s">
         <v>96</v>
@@ -2424,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
